--- a/data/trans_camb/P15A-Edad-trans_camb.xlsx
+++ b/data/trans_camb/P15A-Edad-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-5,25; 0,59</t>
+          <t>-5,26; 0,75</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-5,64; 0,41</t>
+          <t>-6,1; 0,27</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-7,67; -1,2</t>
+          <t>-7,9; -1,21</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-2,26; 1,7</t>
+          <t>-2,03; 1,71</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-2,71; 0,79</t>
+          <t>-2,6; 0,68</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-1,7; 4,8</t>
+          <t>-1,82; 4,63</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-3,07; 0,48</t>
+          <t>-3,1; 0,49</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-3,68; -0,15</t>
+          <t>-3,51; 0,04</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-4,33; 0,46</t>
+          <t>-4,13; 0,05</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-63,13; 14,85</t>
+          <t>-60,6; 18,07</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-67,41; 9,78</t>
+          <t>-69,04; 10,17</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-93,83; -11,61</t>
+          <t>-93,25; -8,41</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-66,85; 134,16</t>
+          <t>-67,43; 113,7</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-84,48; 77,95</t>
+          <t>-82,89; 59,99</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-70,5; 352,19</t>
+          <t>-73,65; 316,55</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-54,73; 15,63</t>
+          <t>-56,5; 14,1</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-64,66; -1,26</t>
+          <t>-64,65; 4,46</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-82,6; 16,57</t>
+          <t>-79,15; 11,32</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-2,36; 2,43</t>
+          <t>-2,11; 2,98</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-3,16; 1,33</t>
+          <t>-3,49; 1,11</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-4,32; 0,98</t>
+          <t>-4,15; 0,94</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-2,79; 1,21</t>
+          <t>-2,79; 0,85</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-3,2; 0,47</t>
+          <t>-3,14; 0,37</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-3,77; -0,31</t>
+          <t>-3,9; -0,4</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-2,16; 1,06</t>
+          <t>-1,88; 1,06</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-2,61; 0,26</t>
+          <t>-2,76; 0,2</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-3,56; -0,52</t>
+          <t>-3,51; -0,47</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-39,6; 70,35</t>
+          <t>-37,08; 80,41</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-54,14; 38,85</t>
+          <t>-59,15; 30,89</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-75,44; 29,37</t>
+          <t>-71,78; 32,46</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-69,01; 74,53</t>
+          <t>-72,13; 46,63</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-78,92; 27,5</t>
+          <t>-77,12; 25,44</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-90,35; -1,94</t>
+          <t>-90,71; -5,0</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-43,04; 33,51</t>
+          <t>-40,77; 33,34</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-56,46; 9,36</t>
+          <t>-56,35; 8,99</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-77,99; -11,75</t>
+          <t>-75,95; -11,56</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-1,68; 1,84</t>
+          <t>-1,95; 1,61</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-1,07; 2,76</t>
+          <t>-1,14; 2,5</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-2,09; 1,34</t>
+          <t>-2,06; 1,41</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-1,62; 1,16</t>
+          <t>-1,79; 1,06</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-1,82; 1,16</t>
+          <t>-1,65; 1,52</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-1,8; 1,0</t>
+          <t>-1,72; 1,15</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-1,38; 0,92</t>
+          <t>-1,29; 1,01</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-0,9; 1,5</t>
+          <t>-0,85; 1,45</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-1,38; 0,74</t>
+          <t>-1,42; 0,8</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-52,83; 139,2</t>
+          <t>-59,88; 116,27</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-34,49; 185,08</t>
+          <t>-37,29; 173,81</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-66,66; 95,41</t>
+          <t>-65,71; 103,24</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-61,62; 133,36</t>
+          <t>-67,83; 90,58</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-68,63; 105,21</t>
+          <t>-65,26; 132,53</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-62,41; 87,46</t>
+          <t>-60,77; 93,94</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-49,7; 59,69</t>
+          <t>-48,48; 67,62</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-35,07; 95,64</t>
+          <t>-34,68; 99,3</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-52,66; 54,57</t>
+          <t>-53,21; 49,0</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-4,73; -0,63</t>
+          <t>-4,72; -0,76</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-4,49; -0,08</t>
+          <t>-4,15; -0,13</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-4,17; 0,86</t>
+          <t>-4,04; 0,82</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-0,63; 3,02</t>
+          <t>-0,67; 3,18</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-2,11; 1,18</t>
+          <t>-1,96; 1,29</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-1,8; 1,08</t>
+          <t>-1,77; 1,05</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-2,02; 0,77</t>
+          <t>-1,93; 0,87</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-2,37; 0,32</t>
+          <t>-2,46; 0,16</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-2,35; 0,52</t>
+          <t>-2,21; 0,69</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-86,11; -8,05</t>
+          <t>-86,95; -25,07</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-80,75; 3,07</t>
+          <t>-78,3; 1,89</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-79,68; 26,96</t>
+          <t>-78,4; 27,69</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-25,76; 277,13</t>
+          <t>-33,05; 300,58</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-71,97; 132,62</t>
+          <t>-70,65; 159,99</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-61,98; 127,64</t>
+          <t>-61,55; 127,57</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-54,8; 37,94</t>
+          <t>-53,34; 44,75</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-64,78; 18,0</t>
+          <t>-65,56; 12,76</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-63,74; 22,46</t>
+          <t>-60,82; 30,76</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-3,39; 0,3</t>
+          <t>-3,54; 0,32</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-3,68; -0,08</t>
+          <t>-3,47; -0,07</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-3,33; 0,23</t>
+          <t>-3,31; 0,33</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-1,65; 2,95</t>
+          <t>-1,74; 2,8</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-1,8; 2,66</t>
+          <t>-1,69; 2,68</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-2,23; 1,44</t>
+          <t>-2,36; 1,43</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-1,97; 1,1</t>
+          <t>-1,79; 1,1</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-2,07; 0,93</t>
+          <t>-1,81; 0,99</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-2,21; 0,37</t>
+          <t>-2,2; 0,4</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-90,28; 48,59</t>
+          <t>-92,03; 49,89</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-92,94; 14,02</t>
+          <t>-92,29; 17,32</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-82,9; 31,16</t>
+          <t>-84,98; 40,39</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-50,17; 209,83</t>
+          <t>-49,12; 185,33</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-56,99; 221,03</t>
+          <t>-51,49; 180,66</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-56,67; 108,88</t>
+          <t>-55,68; 103,88</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-58,01; 73,37</t>
+          <t>-57,38; 66,16</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-63,02; 61,9</t>
+          <t>-57,83; 64,84</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-62,3; 23,15</t>
+          <t>-62,03; 26,49</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-0,95; 3,56</t>
+          <t>-1,27; 3,23</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-2,05; 1,48</t>
+          <t>-2,39; 1,41</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-1,97; 1,66</t>
+          <t>-1,79; 1,76</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-1,58; 3,36</t>
+          <t>-1,56; 3,31</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-0,84; 4,43</t>
+          <t>-1,1; 4,3</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-2,86; 2,45</t>
+          <t>-3,14; 2,28</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-0,49; 2,81</t>
+          <t>-0,55; 2,92</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-0,67; 2,55</t>
+          <t>-0,85; 2,49</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-1,6; 1,49</t>
+          <t>-1,67; 1,59</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-58,34; 536,87</t>
+          <t>-56,63; 510,22</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-82,84; 318,02</t>
+          <t>-86,13; 219,36</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-68,53; 258,26</t>
+          <t>-66,49; 333,63</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-50,55; 206,12</t>
+          <t>-41,81; 214,57</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-27,94; 253,24</t>
+          <t>-32,04; 272,27</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-64,45; 135,86</t>
+          <t>-68,57; 130,07</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>-20,26; 185,09</t>
+          <t>-25,23; 214,93</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-26,94; 183,75</t>
+          <t>-30,84; 174,86</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-50,05; 100,52</t>
+          <t>-49,16; 106,32</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-2,94; 3,7</t>
+          <t>-2,56; 3,76</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-2,95; 3,21</t>
+          <t>-2,62; 3,23</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-2,55; 2,87</t>
+          <t>-2,67; 2,35</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-5,62; 1,68</t>
+          <t>-5,9; 1,57</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-5,28; 2,47</t>
+          <t>-5,4; 2,45</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-3,9; 2,85</t>
+          <t>-4,02; 2,41</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-3,51; 1,72</t>
+          <t>-3,41; 1,58</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-3,14; 2,06</t>
+          <t>-3,27; 1,97</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-2,52; 1,79</t>
+          <t>-2,92; 1,82</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-67,38; 287,54</t>
+          <t>-67,35; 297,45</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-66,42; 265,92</t>
+          <t>-61,48; 277,84</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-54,78; 249,14</t>
+          <t>-59,5; 183,31</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-62,69; 39,05</t>
+          <t>-61,56; 40,65</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-60,91; 51,87</t>
+          <t>-60,14; 55,87</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-41,29; 65,83</t>
+          <t>-42,48; 55,61</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>-53,35; 41,68</t>
+          <t>-53,29; 44,89</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-48,13; 55,79</t>
+          <t>-50,45; 55,95</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-36,11; 54,63</t>
+          <t>-39,91; 48,74</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-1,76; -0,02</t>
+          <t>-1,76; 0,02</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-2,04; -0,33</t>
+          <t>-2,04; -0,25</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-2,58; -0,74</t>
+          <t>-2,55; -0,7</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-0,89; 0,8</t>
+          <t>-0,82; 0,76</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-1,07; 0,52</t>
+          <t>-1,05; 0,4</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>-1,0; 0,68</t>
+          <t>-1,18; 0,4</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>-1,12; 0,13</t>
+          <t>-1,06; 0,19</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>-1,41; -0,17</t>
+          <t>-1,31; -0,11</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>-1,53; -0,32</t>
+          <t>-1,63; -0,36</t>
         </is>
       </c>
     </row>
@@ -2295,47 +2295,47 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>-41,63; -0,17</t>
+          <t>-41,18; 0,8</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>-47,55; -8,93</t>
+          <t>-47,64; -7,48</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>-60,25; -20,85</t>
+          <t>-60,78; -20,66</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>-27,75; 33,67</t>
+          <t>-26,77; 32,33</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>-33,49; 22,16</t>
+          <t>-33,81; 16,35</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>-31,93; 28,88</t>
+          <t>-34,88; 15,43</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>-30,55; 5,15</t>
+          <t>-29,33; 6,66</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>-38,33; -5,57</t>
+          <t>-35,77; -2,64</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>-43,6; -11,16</t>
+          <t>-45,66; -12,64</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P15A-Edad-trans_camb.xlsx
+++ b/data/trans_camb/P15A-Edad-trans_camb.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>-4,87</t>
+          <t>-4,81</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,55</t>
+          <t>0,33</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>-2,27</t>
+          <t>-2,32</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-5,26; 0,75</t>
+          <t>-5,31; 0,52</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-6,1; 0,27</t>
+          <t>-5,72; 0,33</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-7,9; -1,21</t>
+          <t>-7,75; -1,06</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-2,03; 1,71</t>
+          <t>-2,23; 1,53</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-2,6; 0,68</t>
+          <t>-2,74; 0,55</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-1,82; 4,63</t>
+          <t>-2,08; 4,1</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-3,1; 0,49</t>
+          <t>-2,95; 0,65</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-3,51; 0,04</t>
+          <t>-3,64; -0,11</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-4,13; 0,05</t>
+          <t>-4,23; 0,33</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>-71,37%</t>
+          <t>-70,47%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>24,43%</t>
+          <t>14,51%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>-49,36%</t>
+          <t>-50,36%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-60,6; 18,07</t>
+          <t>-64,27; 9,95</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-69,04; 10,17</t>
+          <t>-68,43; 7,4</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-93,25; -8,41</t>
+          <t>-94,85; -1,03</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-67,43; 113,7</t>
+          <t>-71,13; 117,79</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-82,89; 59,99</t>
+          <t>-87,69; 48,31</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-73,65; 316,55</t>
+          <t>-78,85; 294,32</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-56,5; 14,1</t>
+          <t>-53,24; 19,08</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-64,65; 4,46</t>
+          <t>-67,49; -2,82</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-79,15; 11,32</t>
+          <t>-80,16; 19,97</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>-1,97</t>
+          <t>-1,45</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>-1,98</t>
+          <t>-1,96</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>-2,13</t>
+          <t>-1,8</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-2,11; 2,98</t>
+          <t>-2,21; 2,54</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-3,49; 1,11</t>
+          <t>-3,29; 1,14</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-4,15; 0,94</t>
+          <t>-3,85; 1,45</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-2,79; 0,85</t>
+          <t>-2,8; 0,97</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-3,14; 0,37</t>
+          <t>-3,11; 0,44</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-3,9; -0,4</t>
+          <t>-3,64; -0,31</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-1,88; 1,06</t>
+          <t>-1,92; 1,1</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-2,76; 0,2</t>
+          <t>-2,76; 0,08</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-3,51; -0,47</t>
+          <t>-3,21; -0,23</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>-41,55%</t>
+          <t>-30,54%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>-66,72%</t>
+          <t>-65,92%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>-54,26%</t>
+          <t>-45,89%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-37,08; 80,41</t>
+          <t>-38,42; 70,19</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-59,15; 30,89</t>
+          <t>-53,96; 31,54</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-71,78; 32,46</t>
+          <t>-68,88; 46,27</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-72,13; 46,63</t>
+          <t>-71,0; 60,99</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-77,12; 25,44</t>
+          <t>-76,88; 30,6</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-90,71; -5,0</t>
+          <t>-89,67; -5,41</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-40,77; 33,34</t>
+          <t>-40,15; 35,4</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-56,35; 8,99</t>
+          <t>-58,37; 2,89</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-75,95; -11,56</t>
+          <t>-70,67; -1,2</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>-0,44</t>
+          <t>-0,43</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>-0,23</t>
+          <t>-0,29</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>-0,33</t>
+          <t>-0,35</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-1,95; 1,61</t>
+          <t>-1,76; 1,76</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-1,14; 2,5</t>
+          <t>-1,04; 2,62</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-2,06; 1,41</t>
+          <t>-2,11; 1,25</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-1,79; 1,06</t>
+          <t>-1,84; 1,18</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-1,65; 1,52</t>
+          <t>-1,83; 1,27</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-1,72; 1,15</t>
+          <t>-1,79; 0,87</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-1,29; 1,01</t>
+          <t>-1,33; 0,97</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-0,85; 1,45</t>
+          <t>-1,0; 1,32</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-1,42; 0,8</t>
+          <t>-1,42; 0,74</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>-18,88%</t>
+          <t>-18,3%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>-11,68%</t>
+          <t>-14,71%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>-15,33%</t>
+          <t>-16,38%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-59,88; 116,27</t>
+          <t>-55,29; 119,94</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-37,29; 173,81</t>
+          <t>-35,08; 184,57</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-65,71; 103,24</t>
+          <t>-66,61; 94,3</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-67,83; 90,58</t>
+          <t>-66,58; 107,52</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-65,26; 132,53</t>
+          <t>-67,83; 113,48</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-60,77; 93,94</t>
+          <t>-62,56; 76,28</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-48,48; 67,62</t>
+          <t>-49,83; 60,68</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-34,68; 99,3</t>
+          <t>-35,41; 83,3</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-53,21; 49,0</t>
+          <t>-53,03; 46,71</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>-1,33</t>
+          <t>-0,55</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>-0,24</t>
+          <t>-0,13</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>-0,74</t>
+          <t>-0,36</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-4,72; -0,76</t>
+          <t>-4,81; -0,73</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-4,15; -0,13</t>
+          <t>-4,19; 0,13</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-4,04; 0,82</t>
+          <t>-2,81; 1,59</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-0,67; 3,18</t>
+          <t>-0,62; 3,38</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-1,96; 1,29</t>
+          <t>-2,1; 1,32</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-1,77; 1,05</t>
+          <t>-1,9; 1,19</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-1,93; 0,87</t>
+          <t>-1,89; 0,67</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-2,46; 0,16</t>
+          <t>-2,25; 0,18</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-2,21; 0,69</t>
+          <t>-1,64; 0,94</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>-35,3%</t>
+          <t>-14,57%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>-12,68%</t>
+          <t>-7,09%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>-26,31%</t>
+          <t>-12,84%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-86,95; -25,07</t>
+          <t>-86,22; -18,24</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-78,3; 1,89</t>
+          <t>-78,07; 14,17</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-78,4; 27,69</t>
+          <t>-56,85; 68,27</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-33,05; 300,58</t>
+          <t>-30,47; 276,1</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-70,65; 159,99</t>
+          <t>-71,64; 126,24</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-61,55; 127,57</t>
+          <t>-61,55; 125,49</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-53,34; 44,75</t>
+          <t>-54,0; 30,39</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-65,56; 12,76</t>
+          <t>-64,21; 10,08</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-60,82; 30,76</t>
+          <t>-46,19; 47,58</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>-1,25</t>
+          <t>-1,22</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>-0,67</t>
+          <t>-0,66</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-3,54; 0,32</t>
+          <t>-3,48; 0,26</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-3,47; -0,07</t>
+          <t>-3,66; 0,07</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-3,31; 0,33</t>
+          <t>-3,32; 0,51</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-1,74; 2,8</t>
+          <t>-1,76; 2,74</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-1,69; 2,68</t>
+          <t>-1,81; 2,56</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-2,36; 1,43</t>
+          <t>-1,96; 1,48</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-1,79; 1,1</t>
+          <t>-1,84; 1,26</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-1,81; 0,99</t>
+          <t>-1,93; 0,83</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-2,2; 0,4</t>
+          <t>-2,05; 0,43</t>
         </is>
       </c>
     </row>
@@ -1604,7 +1604,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>-51,45%</t>
+          <t>-50,54%</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>-3,53%</t>
+          <t>-3,7%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>-27,69%</t>
+          <t>-27,04%</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-92,03; 49,89</t>
+          <t>-91,77; 46,18</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-92,29; 17,32</t>
+          <t>-92,43; 31,88</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-84,98; 40,39</t>
+          <t>-83,13; 65,23</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-49,12; 185,33</t>
+          <t>-51,57; 185,38</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-51,49; 180,66</t>
+          <t>-56,05; 181,98</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-55,68; 103,88</t>
+          <t>-53,17; 115,43</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-57,38; 66,16</t>
+          <t>-56,07; 78,06</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-57,83; 64,84</t>
+          <t>-58,79; 51,09</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-62,03; 26,49</t>
+          <t>-59,57; 28,07</t>
         </is>
       </c>
     </row>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>0,14</t>
+          <t>0,13</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -1729,7 +1729,7 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>0,1</t>
+          <t>1,61</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -1744,7 +1744,7 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>0,2</t>
+          <t>0,88</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-1,27; 3,23</t>
+          <t>-1,35; 3,24</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-2,39; 1,41</t>
+          <t>-2,24; 1,59</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-1,79; 1,76</t>
+          <t>-1,84; 1,63</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-1,56; 3,31</t>
+          <t>-1,37; 3,55</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-1,1; 4,3</t>
+          <t>-1,05; 4,4</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-3,14; 2,28</t>
+          <t>-0,73; 3,51</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-0,55; 2,92</t>
+          <t>-0,65; 2,76</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-0,85; 2,49</t>
+          <t>-0,91; 2,41</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-1,67; 1,59</t>
+          <t>-0,66; 2,15</t>
         </is>
       </c>
     </row>
@@ -1820,7 +1820,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>8,9%</t>
+          <t>8,16%</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -1835,7 +1835,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>3,67%</t>
+          <t>60,73%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -1850,7 +1850,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>9,38%</t>
+          <t>40,53%</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-56,63; 510,22</t>
+          <t>-63,44; 455,37</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-86,13; 219,36</t>
+          <t>-85,34; 273,08</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-66,49; 333,63</t>
+          <t>-70,31; 272,75</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-41,81; 214,57</t>
+          <t>-38,46; 249,11</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-32,04; 272,27</t>
+          <t>-33,81; 282,23</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-68,57; 130,07</t>
+          <t>-19,48; 229,1</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>-25,23; 214,93</t>
+          <t>-24,97; 212,18</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-30,84; 174,86</t>
+          <t>-32,47; 184,88</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-49,16; 106,32</t>
+          <t>-22,16; 153,64</t>
         </is>
       </c>
     </row>
@@ -1930,7 +1930,7 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>0,21</t>
+          <t>0,3</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -1945,7 +1945,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>-0,44</t>
+          <t>-0,58</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>-0,23</t>
+          <t>-0,29</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-2,56; 3,76</t>
+          <t>-2,75; 3,61</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-2,62; 3,23</t>
+          <t>-2,57; 3,43</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-2,67; 2,35</t>
+          <t>-2,89; 2,88</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-5,9; 1,57</t>
+          <t>-5,58; 1,7</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-5,4; 2,45</t>
+          <t>-5,07; 2,2</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-4,02; 2,41</t>
+          <t>-4,39; 2,33</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-3,41; 1,58</t>
+          <t>-3,51; 1,58</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-3,27; 1,97</t>
+          <t>-3,43; 1,76</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-2,92; 1,82</t>
+          <t>-2,51; 1,92</t>
         </is>
       </c>
     </row>
@@ -2036,7 +2036,7 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>7,46%</t>
+          <t>10,64%</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>-6,51%</t>
+          <t>-8,63%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>-4,42%</t>
+          <t>-5,46%</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-67,35; 297,45</t>
+          <t>-66,49; 281,76</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-61,48; 277,84</t>
+          <t>-59,41; 309,22</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-59,5; 183,31</t>
+          <t>-60,08; 237,32</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-61,56; 40,65</t>
+          <t>-62,15; 40,96</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-60,14; 55,87</t>
+          <t>-59,86; 48,61</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-42,48; 55,61</t>
+          <t>-45,13; 50,82</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>-53,29; 44,89</t>
+          <t>-53,31; 42,7</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-50,45; 55,95</t>
+          <t>-51,74; 42,5</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-39,91; 48,74</t>
+          <t>-36,47; 55,77</t>
         </is>
       </c>
     </row>
@@ -2146,7 +2146,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>-1,65</t>
+          <t>-1,43</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -2161,7 +2161,7 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>-0,28</t>
+          <t>-0,11</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>-0,95</t>
+          <t>-0,76</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-1,76; 0,02</t>
+          <t>-1,75; -0,02</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-2,04; -0,25</t>
+          <t>-2,05; -0,26</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-2,55; -0,7</t>
+          <t>-2,34; -0,52</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-0,82; 0,76</t>
+          <t>-0,78; 0,85</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-1,05; 0,4</t>
+          <t>-1,11; 0,46</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>-1,18; 0,4</t>
+          <t>-0,89; 0,61</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>-1,06; 0,19</t>
+          <t>-1,04; 0,16</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>-1,31; -0,11</t>
+          <t>-1,31; -0,18</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>-1,63; -0,36</t>
+          <t>-1,31; -0,19</t>
         </is>
       </c>
     </row>
@@ -2252,7 +2252,7 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>-43,88%</t>
+          <t>-37,95%</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
@@ -2267,7 +2267,7 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>-10,01%</t>
+          <t>-4,1%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
@@ -2282,7 +2282,7 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>-29,15%</t>
+          <t>-23,25%</t>
         </is>
       </c>
     </row>
@@ -2295,47 +2295,47 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>-41,18; 0,8</t>
+          <t>-41,01; -0,92</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>-47,64; -7,48</t>
+          <t>-47,86; -7,2</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>-60,78; -20,66</t>
+          <t>-55,45; -15,64</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>-26,77; 32,33</t>
+          <t>-24,17; 36,3</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>-33,81; 16,35</t>
+          <t>-34,57; 19,82</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>-34,88; 15,43</t>
+          <t>-27,6; 25,94</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>-29,33; 6,66</t>
+          <t>-28,88; 5,63</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>-35,77; -2,64</t>
+          <t>-36,59; -5,73</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>-45,66; -12,64</t>
+          <t>-36,74; -6,1</t>
         </is>
       </c>
     </row>
